--- a/python项目文件/数据分析/学生成绩数据.xlsx
+++ b/python项目文件/数据分析/学生成绩数据.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4011" uniqueCount="973">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4010" uniqueCount="973">
   <si>
     <t>学号</t>
   </si>
@@ -2958,7 +2958,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2978,13 +2978,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -3455,28 +3448,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3485,118 +3481,115 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4012,7 +4005,7 @@
         <v>61</v>
       </c>
       <c r="H2" s="2">
-        <v>61</v>
+        <v>-61</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>12</v>
@@ -4031,9 +4024,7 @@
       <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="5">
-        <v>88</v>
-      </c>
+      <c r="C3" s="5"/>
       <c r="D3" s="5">
         <v>90</v>
       </c>
@@ -4160,9 +4151,7 @@
       <c r="J6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="K6" s="4"/>
     </row>
     <row r="7" ht="17" customHeight="1" spans="1:11">
       <c r="A7" s="5">
